--- a/public/layoutadjustmentstok_expired.xlsx
+++ b/public/layoutadjustmentstok_expired.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJEK\inventory_bsb\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJEK\PT SYAHID HUSADA DEWATA\inventory_shd\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8744F3-CFFC-43F5-8719-45E055FAD503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD5EE7C-ED2C-45D4-A807-668C48EB3F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lembar1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>kode</t>
   </si>
@@ -45,16 +45,19 @@
     <t>stok total</t>
   </si>
   <si>
-    <t>harga beli</t>
-  </si>
-  <si>
-    <t>diskon_persen</t>
-  </si>
-  <si>
-    <t>diskon_rupiah</t>
-  </si>
-  <si>
-    <t>kode supplier</t>
+    <t>P260001</t>
+  </si>
+  <si>
+    <t>31/06/2027</t>
+  </si>
+  <si>
+    <t>P260002</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>31/05/2027</t>
   </si>
 </sst>
 </file>
@@ -119,11 +122,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,50 +411,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>123456</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>1245678</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="F3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
+      <c r="D4">
+        <v>5478</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
